--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486962_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486962_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4494</v>
+        <v>6.305</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6921</v>
+        <v>8.280900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.2427</v>
+        <v>-1.9759</v>
       </c>
       <c r="G2" t="n">
         <v>5.3505</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9729</v>
+        <v>-0.1172</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.178</v>
+        <v>-0.5891</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2051</v>
+        <v>0.4719</v>
       </c>
       <c r="V2" t="n">
         <v>3.5359</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2725</v>
+        <v>3.2338</v>
       </c>
       <c r="E3" t="n">
-        <v>3.028</v>
+        <v>2.9893</v>
       </c>
       <c r="F3" t="n">
         <v>0.2445</v>
@@ -688,10 +688,10 @@
         <v>0.616</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1899</v>
+        <v>0.1512</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0386</v>
+        <v>-0.0001</v>
       </c>
       <c r="U3" t="n">
         <v>0.1513</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5819</v>
+        <v>0.707</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6705</v>
+        <v>1.7363</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0886</v>
+        <v>-1.0293</v>
       </c>
       <c r="G4" t="n">
         <v>1.4877</v>
@@ -766,13 +766,13 @@
         <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1208</v>
+        <v>0.246</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5542</v>
+        <v>-0.4883</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6751</v>
+        <v>0.7343</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3974</v>
+        <v>0.5522</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2746</v>
+        <v>0.3405</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1228</v>
+        <v>0.2117</v>
       </c>
       <c r="G5" t="n">
         <v>0.6016</v>
@@ -844,13 +844,13 @@
         <v>0.2053</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4095</v>
+        <v>-0.2547</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3294</v>
+        <v>-0.2635</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>C. MARTOS INFANTES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.113</v>
+        <v>0.0107</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0512</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9383</v>
+        <v>0.0107</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7348</v>
+        <v>-0.1947</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2173</v>
+        <v>-0.1947</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9522</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2525</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4896</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7629</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9874</v>
+        <v>-0.1947</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2723</v>
+        <v>-0.1947</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.7151</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5727</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7823</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7903</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0698</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. MARTOS INFANTES</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0107</v>
+        <v>-0.3518</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.8898</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0107</v>
+        <v>0.538</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1947</v>
+        <v>0.4947</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1947</v>
+        <v>-0.0973</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.592</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.8305</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.8439</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.0134</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1947</v>
+        <v>-0.3358</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1947</v>
+        <v>-0.9412</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.6054</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.3856</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.3331</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.0524</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>G. MULERO MALDONADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8814</v>
+        <v>-0.9686</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4787</v>
+        <v>1.0879</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5973000000000001</v>
+        <v>-2.0565</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4947</v>
+        <v>2.7264</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0973</v>
+        <v>2.7605</v>
       </c>
       <c r="I8" t="n">
-        <v>0.592</v>
+        <v>-0.0341</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8305</v>
+        <v>3.4355</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8439</v>
+        <v>3.4489</v>
       </c>
       <c r="L8" t="n">
         <v>-0.0134</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3358</v>
+        <v>-0.709</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9412</v>
+        <v>-0.6883</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6054</v>
+        <v>-0.0207</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2321</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.144</v>
+        <v>0.188</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2558</v>
+        <v>0.1432</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1117</v>
+        <v>0.0447</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. MULERO MALDONADO</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3828</v>
+        <v>-1.2277</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8515</v>
+        <v>-0.0318</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2343</v>
+        <v>-1.1959</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7264</v>
+        <v>-2.5808</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7605</v>
+        <v>-1.2229</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0341</v>
+        <v>-1.3579</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4355</v>
+        <v>0.2938</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4489</v>
+        <v>-0.0871</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0134</v>
+        <v>0.3809</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.709</v>
+        <v>-2.8747</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6883</v>
+        <v>-1.1358</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0207</v>
+        <v>-1.7388</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.4641</v>
+        <v>1.0267</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2262</v>
+        <v>0.3264</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0931</v>
+        <v>-0.3256</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1331</v>
+        <v>0.652</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9582</v>
+        <v>-1.7952</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5548</v>
+        <v>1.0324</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4034</v>
+        <v>-2.8275</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5808</v>
+        <v>-0.7348</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2229</v>
+        <v>0.2173</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3579</v>
+        <v>-0.9522</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2938</v>
+        <v>2.2525</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0871</v>
+        <v>1.4896</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3809</v>
+        <v>0.7629</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8747</v>
+        <v>-2.9874</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1358</v>
+        <v>-1.2723</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7388</v>
+        <v>-1.7151</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0267</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R10" t="n">
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4041</v>
+        <v>0.6645</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8486</v>
+        <v>-0.2365</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4445</v>
+        <v>0.9011</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0698</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3165</v>
+        <v>-2.3849</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8891</v>
+        <v>-0.9278</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4274</v>
+        <v>-1.4571</v>
       </c>
       <c r="G11" t="n">
         <v>0.4053</v>
@@ -1312,13 +1312,13 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2515</v>
+        <v>0.1831</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0195</v>
+        <v>-0.0582</v>
       </c>
       <c r="U11" t="n">
-        <v>0.271</v>
+        <v>0.2413</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3573</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2788</v>
+        <v>-3.4148</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3719</v>
+        <v>-3.6857</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0931</v>
+        <v>0.2709</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1274</v>
@@ -1390,13 +1390,13 @@
         <v>0.616</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3394</v>
+        <v>0.2034</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4997</v>
+        <v>0.1859</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1604</v>
+        <v>0.0175</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.007200000000000983</v>
+        <v>0.6657000000000006</v>
       </c>
       <c r="E13" t="n">
-        <v>9.273400000000002</v>
+        <v>9.9322</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.266300000000001</v>
+        <v>-9.266400000000003</v>
       </c>
       <c r="G13" t="n">
         <v>9.065600000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5788</v>
+        <v>5.578799999999999</v>
       </c>
       <c r="I13" t="n">
         <v>3.4868</v>
@@ -1468,16 +1468,16 @@
         <v>8.2135</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3176</v>
+        <v>1.9763</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.958</v>
+        <v>-1.2991</v>
       </c>
       <c r="U13" t="n">
-        <v>3.2753</v>
+        <v>3.2752</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.109</v>
+        <v>-0.1089999999999995</v>
       </c>
       <c r="W13" t="n">
         <v>6.264699999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.292</v>
+        <v>2.245</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2018</v>
+        <v>3.888</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9098</v>
+        <v>-1.643</v>
       </c>
       <c r="G14" t="n">
         <v>1.456</v>
@@ -1546,13 +1546,13 @@
         <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.012</v>
+        <v>-0.0591</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0272</v>
+        <v>-0.341</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0152</v>
+        <v>0.282</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5893</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8682</v>
+        <v>1.673</v>
       </c>
       <c r="E15" t="n">
-        <v>2.611</v>
+        <v>2.2972</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7429</v>
+        <v>-0.6243</v>
       </c>
       <c r="G15" t="n">
         <v>-0.148</v>
@@ -1624,13 +1624,13 @@
         <v>2.2588</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7841</v>
+        <v>0.5889</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2826</v>
+        <v>-0.0312</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.6201</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>O. ALVARADO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2787</v>
+        <v>1.6609</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0177</v>
+        <v>3.9177</v>
       </c>
       <c r="F16" t="n">
-        <v>1.261</v>
+        <v>-2.2568</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7068</v>
+        <v>2.6653</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6036</v>
+        <v>-0.2077</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3104</v>
+        <v>2.873</v>
       </c>
       <c r="J16" t="n">
-        <v>1.769</v>
+        <v>5.7001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5061</v>
+        <v>1.6225</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2629</v>
+        <v>4.0776</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0623</v>
+        <v>-3.0349</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1098</v>
+        <v>-1.8302</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0475</v>
+        <v>-1.2047</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1879</v>
+        <v>-0.4068</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7246</v>
+        <v>-0.7557</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5367</v>
+        <v>0.3489</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3491</v>
+        <v>-1.4189</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3491</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. ALVARADO RODRIGUEZ</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2564</v>
+        <v>1.629</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1269</v>
+        <v>1.9502</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8705</v>
+        <v>-0.3212</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6653</v>
+        <v>-3.0821</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2077</v>
+        <v>-1.1322</v>
       </c>
       <c r="I17" t="n">
-        <v>2.873</v>
+        <v>-1.9499</v>
       </c>
       <c r="J17" t="n">
-        <v>5.7001</v>
+        <v>-1.1172</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6225</v>
+        <v>-0.3275</v>
       </c>
       <c r="L17" t="n">
-        <v>4.0776</v>
+        <v>-0.7897</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.0349</v>
+        <v>-1.9649</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8302</v>
+        <v>-0.8047</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2047</v>
+        <v>-1.1602</v>
       </c>
       <c r="P17" t="n">
         <v>0.8214</v>
@@ -1780,28 +1780,28 @@
         <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8114</v>
+        <v>-0.2354</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5465</v>
+        <v>-0.0311</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2649</v>
+        <v>-0.2043</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4189</v>
+        <v>4.1252</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.1252</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9125</v>
+        <v>1.3397</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3226</v>
+        <v>0.2269</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4101</v>
+        <v>1.1127</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0821</v>
+        <v>0.7068</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1322</v>
+        <v>-0.6036</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9499</v>
+        <v>1.3104</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1172</v>
+        <v>1.769</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3275</v>
+        <v>0.5061</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7897</v>
+        <v>1.2629</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9649</v>
+        <v>-1.0623</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8047</v>
+        <v>-1.1098</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1602</v>
+        <v>0.0475</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.952</v>
+        <v>-0.1269</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6587</v>
+        <v>-0.5154</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2933</v>
+        <v>0.3885</v>
       </c>
       <c r="V18" t="n">
-        <v>4.1252</v>
+        <v>0.3491</v>
       </c>
       <c r="W18" t="n">
-        <v>4.1252</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1426</v>
+        <v>0.0118</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7381</v>
+        <v>0.3197</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5955</v>
+        <v>-0.3078</v>
       </c>
       <c r="G19" t="n">
         <v>-2.5326</v>
@@ -1936,13 +1936,13 @@
         <v>2.6694</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0057</v>
+        <v>-0.125</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3485</v>
+        <v>-0.0699</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3428</v>
+        <v>-0.0551</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3646</v>
+        <v>-0.913</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0252</v>
+        <v>0.0794</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3394</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7629</v>
@@ -2014,13 +2014,13 @@
         <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6017</v>
+        <v>-0.1501</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4611</v>
+        <v>-0.3565</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1406</v>
+        <v>0.2064</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4525</v>
+        <v>-1.5205</v>
       </c>
       <c r="E21" t="n">
         <v>0.0793</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5318</v>
+        <v>-1.5998</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9995</v>
@@ -2092,13 +2092,13 @@
         <v>2.2588</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3359</v>
+        <v>-0.404</v>
       </c>
       <c r="T21" t="n">
         <v>-0.4147</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0788</v>
+        <v>0.0108</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3491</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.401</v>
+        <v>-2.497</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7053</v>
+        <v>-1.4961</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6957</v>
+        <v>-1.0009</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3871</v>
@@ -2170,13 +2170,13 @@
         <v>1.8481</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1996</v>
+        <v>0.1037</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5928</v>
+        <v>-0.3836</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7925</v>
+        <v>0.4873</v>
       </c>
       <c r="V22" t="n">
         <v>-2.0082</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5393</v>
+        <v>-2.9386</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1006</v>
+        <v>-1.996</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4386</v>
+        <v>-0.9426</v>
       </c>
       <c r="G23" t="n">
         <v>-4.9813</v>
@@ -2248,13 +2248,13 @@
         <v>1.8481</v>
       </c>
       <c r="S23" t="n">
-        <v>0.594</v>
+        <v>0.1947</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4806</v>
+        <v>-0.376</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0746</v>
+        <v>0.5707</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.007000000000000561</v>
+        <v>0.6903000000000006</v>
       </c>
       <c r="E24" t="n">
         <v>9.266299999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.273299999999999</v>
+        <v>-8.5761</v>
       </c>
       <c r="G24" t="n">
         <v>-9.0654</v>
@@ -2305,7 +2305,7 @@
         <v>8.017300000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>6.3645</v>
+        <v>6.364500000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-23.4472</v>
@@ -2326,13 +2326,13 @@
         <v>18.4809</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3175</v>
+        <v>-0.6200000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-3.2751</v>
       </c>
       <c r="U24" t="n">
-        <v>1.9577</v>
+        <v>2.6553</v>
       </c>
       <c r="V24" t="n">
         <v>0.1088000000000005</v>
